--- a/src/fst/morphology/incoming/stem_spreadsheets/prestem-allomorphs.xlsx
+++ b/src/fst/morphology/incoming/stem_spreadsheets/prestem-allomorphs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\katie\lang-bla\src\fst\morphology\incoming\stem_spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6FDA313-0E6E-4672-A3E8-B7B9413F30EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1AC37E7-C398-4075-906B-ED771978DABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{970177AD-0508-4146-8104-696C4F0D0384}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{970177AD-0508-4146-8104-696C4F0D0384}"/>
   </bookViews>
   <sheets>
     <sheet name="general prestems" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2496" uniqueCount="1164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2496" uniqueCount="1165">
   <si>
     <t>ohko</t>
   </si>
@@ -2949,9 +2949,6 @@
     <t>PS/ksisttoyi</t>
   </si>
   <si>
-    <t>y2ámoohk</t>
-  </si>
-  <si>
     <t>perhaps more nominal</t>
   </si>
   <si>
@@ -3532,6 +3529,12 @@
   </si>
   <si>
     <t>cf mi'ki</t>
+  </si>
+  <si>
+    <t>i2ámoohk</t>
+  </si>
+  <si>
+    <t>VLV a? i2, combine naam?</t>
   </si>
 </sst>
 </file>
@@ -4050,13 +4053,13 @@
         <v>710</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>238</v>
@@ -4096,7 +4099,7 @@
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="H6" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4143,16 +4146,16 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>238</v>
@@ -4269,10 +4272,10 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>78</v>
@@ -4285,7 +4288,7 @@
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="1" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="H12" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4458,23 +4461,23 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>1144</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>1145</v>
-      </c>
       <c r="C18" s="1" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="H18" s="1" t="str">
         <f t="shared" si="0"/>
@@ -4653,16 +4656,16 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>1140</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>1141</v>
-      </c>
       <c r="C24" s="1" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>238</v>
@@ -5034,23 +5037,23 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="H36" s="1" t="str">
         <f t="shared" si="3"/>
@@ -5067,25 +5070,25 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>1107</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="D37" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>1108</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>1108</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>1160</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>1109</v>
       </c>
       <c r="H37" s="1" t="str">
         <f t="shared" si="3"/>
@@ -9736,17 +9739,17 @@
     </row>
     <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F193" s="2"/>
       <c r="G193" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H193" s="1" t="str">
         <f t="shared" si="22"/>
@@ -9766,13 +9769,13 @@
         <v>966</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>238</v>
@@ -9799,14 +9802,14 @@
         <v>966</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F195" s="2"/>
       <c r="G195" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H195" s="1" t="str">
         <f t="shared" si="22"/>
@@ -9848,17 +9851,17 @@
     </row>
     <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F197" s="2"/>
       <c r="G197" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H197" s="1" t="str">
         <f t="shared" si="22"/>
@@ -10007,13 +10010,13 @@
         <v>967</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>238</v>
@@ -10100,20 +10103,20 @@
         <v>968</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F205" s="2"/>
       <c r="G205" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H205" s="1" t="str">
         <f t="shared" si="22"/>
@@ -10163,16 +10166,16 @@
     </row>
     <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B207" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="C207" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="C207" s="1" t="s">
+      <c r="D207" s="1" t="s">
         <v>983</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>984</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>238</v>
@@ -10436,16 +10439,16 @@
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B216" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="C216" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="C216" s="1" t="s">
-        <v>986</v>
-      </c>
       <c r="D216" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>238</v>
@@ -10529,16 +10532,16 @@
     </row>
     <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>238</v>
@@ -10628,23 +10631,23 @@
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B222" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="C222" s="1" t="s">
         <v>989</v>
       </c>
-      <c r="C222" s="1" t="s">
-        <v>990</v>
-      </c>
       <c r="D222" s="1" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F222" s="2"/>
       <c r="G222" s="1" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H222" s="1" t="str">
         <f t="shared" si="26"/>
@@ -10661,23 +10664,23 @@
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F223" s="2"/>
       <c r="G223" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H223" s="1" t="str">
         <f t="shared" si="26"/>
@@ -10727,16 +10730,16 @@
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B225" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="C225" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="C225" s="1" t="s">
-        <v>1001</v>
-      </c>
       <c r="D225" s="1" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>238</v>
@@ -10913,23 +10916,23 @@
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B231" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="C231" s="1" t="s">
         <v>998</v>
       </c>
-      <c r="C231" s="1" t="s">
-        <v>999</v>
-      </c>
       <c r="D231" s="1" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F231" s="2"/>
       <c r="G231" s="1" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H231" s="1" t="str">
         <f t="shared" si="26"/>
@@ -11055,17 +11058,17 @@
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F236" s="2"/>
       <c r="G236" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H236" s="1" t="str">
         <f t="shared" si="26"/>
@@ -11112,17 +11115,17 @@
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F238" s="2"/>
       <c r="G238" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H238" s="1" t="str">
         <f t="shared" ref="H238:H246" si="29">_xlfn.CONCAT(A238,"+:",B238,CHAR(9),E238," ;")</f>
@@ -11299,23 +11302,23 @@
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B245" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C245" s="1" t="s">
         <v>1015</v>
       </c>
-      <c r="C245" s="1" t="s">
-        <v>1016</v>
-      </c>
       <c r="D245" s="1" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F245" s="2"/>
       <c r="G245" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="H245" s="1" t="str">
         <f t="shared" si="29"/>
@@ -11384,16 +11387,16 @@
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B248" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C248" s="1" t="s">
         <v>1033</v>
       </c>
-      <c r="C248" s="1" t="s">
-        <v>1034</v>
-      </c>
       <c r="D248" s="1" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>238</v>
@@ -11417,16 +11420,16 @@
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>238</v>
@@ -11447,17 +11450,17 @@
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F250" s="2"/>
       <c r="G250" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H250" s="1" t="str">
         <f t="shared" si="30"/>
@@ -11518,23 +11521,23 @@
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F253" s="2"/>
       <c r="G253" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="H253" s="1" t="str">
         <f t="shared" si="30"/>
@@ -11920,16 +11923,16 @@
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B267" s="1" t="s">
         <v>1039</v>
       </c>
-      <c r="B267" s="1" t="s">
-        <v>1040</v>
-      </c>
       <c r="C267" s="1" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E267" s="2" t="s">
         <v>238</v>
@@ -11950,16 +11953,16 @@
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="E268" s="2" t="s">
         <v>238</v>
@@ -12059,16 +12062,16 @@
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>238</v>
@@ -12089,10 +12092,10 @@
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B273" s="1" t="s">
         <v>1030</v>
-      </c>
-      <c r="B273" s="1" t="s">
-        <v>1031</v>
       </c>
       <c r="E273" s="2" t="s">
         <v>238</v>
@@ -12113,23 +12116,23 @@
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F274" s="2"/>
       <c r="G274" s="1" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="H274" s="1" t="str">
         <f t="shared" si="30"/>
@@ -12255,23 +12258,23 @@
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F279" s="2"/>
       <c r="G279" s="1" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="H279" s="1" t="str">
         <f t="shared" si="30"/>
@@ -12435,16 +12438,16 @@
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B285" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C285" s="1" t="s">
         <v>1055</v>
       </c>
-      <c r="C285" s="1" t="s">
-        <v>1056</v>
-      </c>
       <c r="D285" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="E285" s="2" t="s">
         <v>238</v>
@@ -12465,10 +12468,10 @@
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="E286" s="2" t="s">
         <v>238</v>
@@ -12481,16 +12484,16 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="E287" s="2" t="s">
         <v>238</v>
@@ -12514,16 +12517,16 @@
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B288" s="1" t="s">
         <v>1036</v>
       </c>
-      <c r="B288" s="1" t="s">
-        <v>1037</v>
-      </c>
       <c r="C288" s="1" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>238</v>
@@ -12580,16 +12583,16 @@
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="E290" s="2" t="s">
         <v>238</v>
@@ -12673,16 +12676,16 @@
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="E293" s="2" t="s">
         <v>238</v>
@@ -12706,16 +12709,16 @@
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="E294" s="2" t="s">
         <v>238</v>
@@ -12805,16 +12808,16 @@
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="E297" s="2" t="s">
         <v>238</v>
@@ -12898,16 +12901,16 @@
     </row>
     <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>238</v>
@@ -12928,16 +12931,16 @@
     </row>
     <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E301" s="2" t="s">
         <v>238</v>
@@ -12961,23 +12964,23 @@
     </row>
     <row r="302" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B302" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C302" s="1" t="s">
         <v>1008</v>
       </c>
-      <c r="C302" s="1" t="s">
-        <v>1009</v>
-      </c>
       <c r="D302" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="E302" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F302" s="2"/>
       <c r="G302" s="1" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="H302" s="1" t="str">
         <f t="shared" si="30"/>
@@ -12994,16 +12997,16 @@
     </row>
     <row r="303" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="E303" s="2" t="s">
         <v>238</v>
@@ -13054,16 +13057,16 @@
     </row>
     <row r="305" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B305" s="1" t="s">
         <v>1071</v>
       </c>
-      <c r="B305" s="1" t="s">
-        <v>1072</v>
-      </c>
       <c r="C305" s="1" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="E305" s="2" t="s">
         <v>238</v>
@@ -13429,16 +13432,16 @@
     </row>
     <row r="317" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="E317" s="2" t="s">
         <v>238</v>
@@ -13495,16 +13498,16 @@
     </row>
     <row r="319" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="E319" s="2" t="s">
         <v>238</v>
@@ -13915,17 +13918,17 @@
         <v>582</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="E332" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F332" s="2"/>
       <c r="G332" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="H332" s="1" t="str">
         <f t="shared" si="39"/>
@@ -14191,16 +14194,16 @@
     </row>
     <row r="341" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="E341" s="2" t="s">
         <v>238</v>
@@ -14221,16 +14224,16 @@
     </row>
     <row r="342" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B342" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="E342" s="2" t="s">
         <v>238</v>
@@ -14503,16 +14506,16 @@
     </row>
     <row r="351" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="E351" s="2" t="s">
         <v>238</v>
@@ -14675,16 +14678,16 @@
     </row>
     <row r="357" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="E357" s="2" t="s">
         <v>238</v>
@@ -14708,17 +14711,17 @@
     </row>
     <row r="358" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B358" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="E358" s="2" t="s">
         <v>907</v>
       </c>
       <c r="F358" s="2"/>
       <c r="G358" s="1" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H358" s="1" t="str">
         <f t="shared" si="39"/>
@@ -15063,16 +15066,16 @@
     </row>
     <row r="370" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B370" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="D370" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="E370" s="2" t="s">
         <v>238</v>
@@ -15342,16 +15345,16 @@
     </row>
     <row r="379" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B379" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="E379" s="2" t="s">
         <v>238</v>
@@ -15372,16 +15375,16 @@
     </row>
     <row r="380" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B380" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="D380" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="E380" s="2" t="s">
         <v>238</v>
@@ -15531,16 +15534,16 @@
     </row>
     <row r="385" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B385" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E385" s="2" t="s">
         <v>238</v>
@@ -15564,16 +15567,16 @@
     </row>
     <row r="386" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B386" s="1" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="E386" s="2" t="s">
         <v>238</v>
@@ -15594,16 +15597,16 @@
     </row>
     <row r="387" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B387" s="1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="E387" s="2" t="s">
         <v>238</v>
@@ -15627,17 +15630,17 @@
     </row>
     <row r="388" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E388" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F388" s="2"/>
       <c r="G388" s="1" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H388" s="1" t="str">
         <f t="shared" si="44"/>
@@ -15992,16 +15995,16 @@
     </row>
     <row r="401" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B401" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C401" s="1" t="s">
         <v>1094</v>
       </c>
-      <c r="C401" s="1" t="s">
-        <v>1095</v>
-      </c>
       <c r="D401" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="E401" s="2" t="s">
         <v>238</v>
@@ -16022,16 +16025,16 @@
     </row>
     <row r="402" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B402" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="D402" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="E402" s="2" t="s">
         <v>238</v>
@@ -16052,10 +16055,10 @@
     </row>
     <row r="403" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B403" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="E403" s="2" t="s">
         <v>238</v>
@@ -16068,16 +16071,16 @@
     </row>
     <row r="404" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B404" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C404" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="D404" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="E404" s="2" t="s">
         <v>238</v>
@@ -16098,10 +16101,10 @@
     </row>
     <row r="405" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B405" s="1" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="E405" s="2" t="s">
         <v>238</v>
@@ -16297,16 +16300,16 @@
     </row>
     <row r="412" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B412" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="C412" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="D412" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="E412" s="2" t="s">
         <v>238</v>
@@ -16360,16 +16363,16 @@
     </row>
     <row r="414" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B414" s="1" t="s">
         <v>1112</v>
       </c>
-      <c r="B414" s="1" t="s">
-        <v>1113</v>
-      </c>
       <c r="C414" s="1" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="E414" s="2" t="s">
         <v>238</v>
@@ -16390,16 +16393,16 @@
     </row>
     <row r="415" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B415" s="1" t="s">
         <v>1114</v>
       </c>
-      <c r="B415" s="1" t="s">
-        <v>1115</v>
-      </c>
       <c r="C415" s="1" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="D415" s="1" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="E415" s="2" t="s">
         <v>238</v>
@@ -16423,16 +16426,16 @@
     </row>
     <row r="416" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B416" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C416" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="E416" s="2" t="s">
         <v>238</v>
@@ -16456,23 +16459,23 @@
     </row>
     <row r="417" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B417" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="C417" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="D417" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E417" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F417" s="2"/>
       <c r="G417" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="H417" s="1" t="str">
         <f t="shared" si="44"/>
@@ -16522,16 +16525,16 @@
     </row>
     <row r="419" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B419" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="C419" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="E419" s="2" t="s">
         <v>238</v>
@@ -16555,16 +16558,16 @@
     </row>
     <row r="420" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="B420" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C420" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="D420" s="1" t="s">
         <v>1126</v>
-      </c>
-      <c r="C420" s="1" t="s">
-        <v>1126</v>
-      </c>
-      <c r="D420" s="1" t="s">
-        <v>1127</v>
       </c>
       <c r="E420" s="2" t="s">
         <v>238</v>
@@ -16753,16 +16756,16 @@
     </row>
     <row r="426" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B426" s="1" t="s">
         <v>1129</v>
       </c>
-      <c r="B426" s="1" t="s">
-        <v>1130</v>
-      </c>
       <c r="C426" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="D426" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="E426" s="2" t="s">
         <v>238</v>
@@ -16852,16 +16855,16 @@
     </row>
     <row r="429" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="B429" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C429" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="D429" s="1" t="s">
         <v>1131</v>
-      </c>
-      <c r="C429" s="1" t="s">
-        <v>1131</v>
-      </c>
-      <c r="D429" s="1" t="s">
-        <v>1132</v>
       </c>
       <c r="E429" s="2" t="s">
         <v>238</v>
@@ -16948,16 +16951,16 @@
     </row>
     <row r="432" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="B432" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C432" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D432" s="1" t="s">
         <v>1133</v>
-      </c>
-      <c r="C432" s="1" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D432" s="1" t="s">
-        <v>1134</v>
       </c>
       <c r="E432" s="2" t="s">
         <v>238</v>
@@ -17176,16 +17179,16 @@
     </row>
     <row r="439" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B439" s="1" t="s">
         <v>1135</v>
       </c>
-      <c r="B439" s="1" t="s">
-        <v>1136</v>
-      </c>
       <c r="C439" s="1" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="D439" s="1" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="E439" s="2" t="s">
         <v>238</v>
@@ -17206,16 +17209,16 @@
     </row>
     <row r="440" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="C440" s="1" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="D440" s="1" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="E440" s="2" t="s">
         <v>238</v>
@@ -17315,7 +17318,7 @@
       </c>
       <c r="F443" s="2"/>
       <c r="G443" s="1" t="s">
-        <v>458</v>
+        <v>1164</v>
       </c>
       <c r="H443" s="1" t="str">
         <f t="shared" si="49"/>
@@ -17335,14 +17338,14 @@
         <v>965</v>
       </c>
       <c r="D444" s="1" t="s">
-        <v>969</v>
+        <v>1163</v>
       </c>
       <c r="E444" s="2" t="s">
         <v>238</v>
       </c>
       <c r="F444" s="2"/>
       <c r="G444" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H444" s="1" t="str">
         <f t="shared" si="49"/>
@@ -17354,7 +17357,7 @@
       </c>
       <c r="J444" s="1" t="str">
         <f t="shared" si="48"/>
-        <v>PS/yámoohk+:y2ámoohk	PSBOUND2 ;</v>
+        <v>PS/yámoohk+:i2ámoohk	PSBOUND2 ;</v>
       </c>
     </row>
     <row r="445" spans="1:10" x14ac:dyDescent="0.25">
@@ -17435,16 +17438,16 @@
     </row>
     <row r="448" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="D448" s="1" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="E448" s="2" t="s">
         <v>238</v>
@@ -17501,16 +17504,16 @@
     </row>
     <row r="450" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D450" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="E450" s="2" t="s">
         <v>238</v>
@@ -17610,7 +17613,7 @@
         <v>237</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>109</v>
@@ -17896,7 +17899,7 @@
         <v>237</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>109</v>
@@ -17978,7 +17981,7 @@
         <v>203</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>204</v>
@@ -18063,7 +18066,7 @@
         <v>237</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>109</v>
@@ -18106,16 +18109,16 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>1143</v>
-      </c>
       <c r="C3" s="1" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="H3" s="1" t="str">
         <f t="shared" ref="H3:H4" si="0">_xlfn.CONCAT(A3,"+:",B3,CHAR(9),"PSBOUND1 ;")</f>
